--- a/40000-60000.xlsx
+++ b/40000-60000.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="116">
   <si>
     <t>CVR</t>
   </si>
@@ -211,6 +211,12 @@
     <t>61552812</t>
   </si>
   <si>
+    <t>15603712</t>
+  </si>
+  <si>
+    <t>38235311</t>
+  </si>
+  <si>
     <t>BPO Visma Løn og HR</t>
   </si>
   <si>
@@ -247,6 +253,9 @@
     <t>Visma Løn (Fehmarn Belt Contractors I/S)</t>
   </si>
   <si>
+    <t>Løn &amp; HR</t>
+  </si>
+  <si>
     <t>Strategisk beslutning</t>
   </si>
   <si>
@@ -347,6 +356,9 @@
   </si>
   <si>
     <t>2024Q3</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
   </si>
   <si>
     <t>40000-60000</t>
@@ -711,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -754,19 +766,19 @@
         <v>52126.72</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2">
         <v>44209</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -780,22 +792,22 @@
         <v>50524.99</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="2">
         <v>44217</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -809,22 +821,22 @@
         <v>59748.16</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" s="2">
         <v>44229</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -838,22 +850,22 @@
         <v>56812.75</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2">
         <v>44235</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -867,19 +879,19 @@
         <v>48008.41</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2">
         <v>44279</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -893,19 +905,19 @@
         <v>42997.07</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2">
         <v>44299</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -919,19 +931,19 @@
         <v>51618.2</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="2">
         <v>44315</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -945,19 +957,19 @@
         <v>51608.6</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2">
         <v>44368</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -971,19 +983,19 @@
         <v>49192.74</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2">
         <v>44375</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -997,22 +1009,22 @@
         <v>47508</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2">
         <v>44376</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1026,19 +1038,19 @@
         <v>48167</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2">
         <v>44376</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1052,22 +1064,22 @@
         <v>48600</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2">
         <v>44371</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1081,19 +1093,19 @@
         <v>54307</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2">
         <v>44382</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1107,19 +1119,19 @@
         <v>59696</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2">
         <v>44531</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1133,19 +1145,19 @@
         <v>55692.36</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2">
         <v>44540</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1159,19 +1171,19 @@
         <v>58860</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2">
         <v>44553</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1185,22 +1197,22 @@
         <v>44529.04</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2">
         <v>44583</v>
       </c>
       <c r="F18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I18" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1214,19 +1226,19 @@
         <v>44071.91</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2">
         <v>44593</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1240,19 +1252,19 @@
         <v>59444.88</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>44600</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1266,19 +1278,19 @@
         <v>46500</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2">
         <v>44637</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1292,19 +1304,19 @@
         <v>50075</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="2">
         <v>44645</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1318,19 +1330,19 @@
         <v>44929.04</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" s="2">
         <v>44655</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1344,19 +1356,19 @@
         <v>58657</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2">
         <v>44685</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1370,19 +1382,19 @@
         <v>44851</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2">
         <v>44719</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1396,19 +1408,19 @@
         <v>41918.41</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2">
         <v>44742</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1422,19 +1434,19 @@
         <v>53378.16</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2">
         <v>44749</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1448,19 +1460,19 @@
         <v>40191.95</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2">
         <v>44753</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1474,19 +1486,19 @@
         <v>57060</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2">
         <v>44784</v>
       </c>
       <c r="F29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I29" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1500,19 +1512,19 @@
         <v>48312</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2">
         <v>44833</v>
       </c>
       <c r="F30" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1526,19 +1538,19 @@
         <v>47117</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2">
         <v>44862</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I31" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1552,19 +1564,19 @@
         <v>42583</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2">
         <v>44872</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I32" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1578,19 +1590,19 @@
         <v>44550</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2">
         <v>44894</v>
       </c>
       <c r="F33" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I33" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1604,19 +1616,19 @@
         <v>50482.04</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2">
         <v>44831</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I34" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1630,19 +1642,19 @@
         <v>52852.17</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E35" s="2">
         <v>44936</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1656,16 +1668,16 @@
         <v>43967</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E36" s="2">
         <v>44904</v>
       </c>
       <c r="H36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I36" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1679,16 +1691,16 @@
         <v>58165</v>
       </c>
       <c r="D37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E37" s="2">
         <v>45009</v>
       </c>
       <c r="H37" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I37" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1702,16 +1714,16 @@
         <v>57600</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2">
         <v>45072</v>
       </c>
       <c r="H38" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1725,16 +1737,16 @@
         <v>46106</v>
       </c>
       <c r="D39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2">
         <v>45091</v>
       </c>
       <c r="H39" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I39" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1748,16 +1760,16 @@
         <v>44064</v>
       </c>
       <c r="D40" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2">
         <v>45092</v>
       </c>
       <c r="H40" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1771,16 +1783,16 @@
         <v>58800</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2">
         <v>45167</v>
       </c>
       <c r="H41" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1794,19 +1806,19 @@
         <v>44547</v>
       </c>
       <c r="D42" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2">
         <v>45177</v>
       </c>
       <c r="G42" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H42" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I42" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1820,19 +1832,19 @@
         <v>40172</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E43" s="2">
         <v>45243</v>
       </c>
       <c r="G43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I43" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1846,16 +1858,16 @@
         <v>40892</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E44" s="2">
         <v>45272</v>
       </c>
       <c r="H44" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I44" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1869,16 +1881,16 @@
         <v>40925</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E45" s="2">
         <v>45301</v>
       </c>
       <c r="H45" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I45" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1892,16 +1904,16 @@
         <v>59316</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E46" s="2">
         <v>45345</v>
       </c>
       <c r="H46" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1915,16 +1927,16 @@
         <v>47491.62</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E47" s="2">
         <v>45370</v>
       </c>
       <c r="H47" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1938,16 +1950,16 @@
         <v>50892</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2">
         <v>45400</v>
       </c>
       <c r="H48" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I48" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1961,19 +1973,19 @@
         <v>49332</v>
       </c>
       <c r="D49" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E49" s="2">
         <v>45433</v>
       </c>
       <c r="G49" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H49" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I49" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1987,16 +1999,16 @@
         <v>40956</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2">
         <v>45329</v>
       </c>
       <c r="H50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I50" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2010,16 +2022,16 @@
         <v>59832</v>
       </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E51" s="2">
         <v>45446</v>
       </c>
       <c r="H51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I51" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2033,19 +2045,19 @@
         <v>50400</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E52" s="2">
         <v>45447</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I52" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2059,16 +2071,16 @@
         <v>55116</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E53" s="2">
         <v>45488</v>
       </c>
       <c r="H53" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I53" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2082,16 +2094,16 @@
         <v>41460</v>
       </c>
       <c r="D54" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2">
         <v>45516</v>
       </c>
       <c r="H54" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2105,16 +2117,16 @@
         <v>40152</v>
       </c>
       <c r="D55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E55" s="2">
         <v>45467</v>
       </c>
       <c r="H55" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I55" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2128,16 +2140,16 @@
         <v>49752</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E56" s="2">
         <v>45526</v>
       </c>
       <c r="H56" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I56" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2151,16 +2163,62 @@
         <v>53700</v>
       </c>
       <c r="D57" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2">
         <v>45546</v>
       </c>
       <c r="H57" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I57" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>2024</v>
+      </c>
+      <c r="C58">
+        <v>49680</v>
+      </c>
+      <c r="D58" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45579</v>
+      </c>
+      <c r="H58" t="s">
+        <v>114</v>
+      </c>
+      <c r="I58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59">
+        <v>2024</v>
+      </c>
+      <c r="C59">
+        <v>48204</v>
+      </c>
+      <c r="D59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45428</v>
+      </c>
+      <c r="H59" t="s">
+        <v>112</v>
+      </c>
+      <c r="I59" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
